--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487167_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487167_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>12.591</v>
+        <v>10.4465</v>
       </c>
       <c r="E2" t="n">
-        <v>10.9089</v>
+        <v>9.165900000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>1.6821</v>
+        <v>1.2806</v>
       </c>
       <c r="G2" t="n">
         <v>4.8539</v>
@@ -610,13 +610,13 @@
         <v>2.7021</v>
       </c>
       <c r="S2" t="n">
-        <v>4.5708</v>
+        <v>2.4262</v>
       </c>
       <c r="T2" t="n">
-        <v>3.0816</v>
+        <v>1.3386</v>
       </c>
       <c r="U2" t="n">
-        <v>1.4891</v>
+        <v>1.0876</v>
       </c>
       <c r="V2" t="n">
         <v>1.4293</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.9805</v>
+        <v>9.1822</v>
       </c>
       <c r="E3" t="n">
-        <v>6.7963</v>
+        <v>7.7571</v>
       </c>
       <c r="F3" t="n">
-        <v>1.1842</v>
+        <v>1.4251</v>
       </c>
       <c r="G3" t="n">
         <v>3.4409</v>
@@ -688,13 +688,13 @@
         <v>2.7021</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.5532</v>
+        <v>0.6484</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.0575</v>
+        <v>-0.0968</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5043</v>
+        <v>0.7452</v>
       </c>
       <c r="V3" t="n">
         <v>3.3558</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>6.0434</v>
+        <v>7.4662</v>
       </c>
       <c r="E4" t="n">
-        <v>4.4017</v>
+        <v>5.5032</v>
       </c>
       <c r="F4" t="n">
-        <v>1.6417</v>
+        <v>1.963</v>
       </c>
       <c r="G4" t="n">
         <v>4.7872</v>
@@ -766,13 +766,13 @@
         <v>2.3161</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3807</v>
+        <v>1.0421</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5671</v>
+        <v>0.5345</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1864</v>
+        <v>0.5076000000000001</v>
       </c>
       <c r="V4" t="n">
         <v>0.2859</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.461</v>
+        <v>3.1477</v>
       </c>
       <c r="E5" t="n">
-        <v>4.4407</v>
+        <v>3.94</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.9797</v>
+        <v>-0.7923</v>
       </c>
       <c r="G5" t="n">
         <v>0.853</v>
@@ -844,13 +844,13 @@
         <v>2.3161</v>
       </c>
       <c r="S5" t="n">
-        <v>1.1918</v>
+        <v>0.8784999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8871</v>
+        <v>0.3864</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3047</v>
+        <v>0.4921</v>
       </c>
       <c r="V5" t="n">
         <v>-0.8999</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2251</v>
+        <v>1.3639</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5491</v>
+        <v>0.7682</v>
       </c>
       <c r="F6" t="n">
-        <v>0.676</v>
+        <v>0.5957</v>
       </c>
       <c r="G6" t="n">
         <v>0.5806</v>
@@ -922,13 +922,13 @@
         <v>0.579</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0654</v>
+        <v>0.2042</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0449</v>
+        <v>0.1742</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1104</v>
+        <v>0.0301</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. TOURE</t>
+          <t>J. TEJERINA TEJEDO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.268</v>
+        <v>-0.1172</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.5281</v>
+        <v>-2.3789</v>
       </c>
       <c r="F7" t="n">
-        <v>1.796</v>
+        <v>2.2616</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.7689</v>
+        <v>-3.2022</v>
       </c>
       <c r="H7" t="n">
-        <v>-3.1858</v>
+        <v>-2.2376</v>
       </c>
       <c r="I7" t="n">
-        <v>0.417</v>
+        <v>-0.9646</v>
       </c>
       <c r="J7" t="n">
-        <v>-2.4353</v>
+        <v>-1.8336</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.5981</v>
+        <v>-0.4813</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1628</v>
+        <v>-1.3523</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3336</v>
+        <v>-1.3685</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5878</v>
+        <v>-1.7562</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2542</v>
+        <v>0.3877</v>
       </c>
       <c r="P7" t="n">
         <v>0.965</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.965</v>
       </c>
       <c r="R7" t="n">
-        <v>0.965</v>
+        <v>1.9301</v>
       </c>
       <c r="S7" t="n">
-        <v>1.7437</v>
+        <v>0.8074</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6214</v>
+        <v>0.4198</v>
       </c>
       <c r="U7" t="n">
-        <v>1.1223</v>
+        <v>0.3876</v>
       </c>
       <c r="V7" t="n">
-        <v>0.3281</v>
+        <v>1.3125</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2859</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0422</v>
+        <v>1.3125</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. TEJERINA TEJEDO</t>
+          <t>A. TOURE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4573</v>
+        <v>-0.4548</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.6387</v>
+        <v>-1.769</v>
       </c>
       <c r="F8" t="n">
-        <v>2.1813</v>
+        <v>1.3142</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.2022</v>
+        <v>-2.7689</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.2376</v>
+        <v>-3.1858</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.9646</v>
+        <v>0.417</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.8336</v>
+        <v>-2.4353</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.4813</v>
+        <v>-2.5981</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.3523</v>
+        <v>0.1628</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.3685</v>
+        <v>-0.3336</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.7562</v>
+        <v>-0.5878</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3877</v>
+        <v>0.2542</v>
       </c>
       <c r="P8" t="n">
         <v>0.965</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.9301</v>
+        <v>0.965</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4673</v>
+        <v>1.0209</v>
       </c>
       <c r="T8" t="n">
-        <v>0.16</v>
+        <v>0.3804</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3073</v>
+        <v>0.6405</v>
       </c>
       <c r="V8" t="n">
-        <v>1.3125</v>
+        <v>0.3281</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.2859</v>
       </c>
       <c r="X8" t="n">
-        <v>1.3125</v>
+        <v>0.0422</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.0358</v>
+        <v>-0.8702</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.1529</v>
+        <v>-0.9338</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1171</v>
+        <v>0.0635</v>
       </c>
       <c r="G9" t="n">
         <v>-1.8128</v>
@@ -1156,13 +1156,13 @@
         <v>0.965</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0978</v>
+        <v>0.2634</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3278</v>
+        <v>-0.1087</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4257</v>
+        <v>0.3721</v>
       </c>
       <c r="V9" t="n">
         <v>-0.2859</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.4258</v>
+        <v>-1.287</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.3966</v>
+        <v>-1.1774</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.0293</v>
+        <v>-0.1096</v>
       </c>
       <c r="G10" t="n">
         <v>-1.4986</v>
@@ -1234,13 +1234,13 @@
         <v>0.579</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0654</v>
+        <v>0.2042</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0449</v>
+        <v>0.1742</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1104</v>
+        <v>0.0301</v>
       </c>
       <c r="V10" t="n">
         <v>-0.5717</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.3505</v>
+        <v>-2.9778</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.2505</v>
+        <v>-0.9313</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.1</v>
+        <v>-2.0465</v>
       </c>
       <c r="G11" t="n">
         <v>-0.4707</v>
@@ -1312,13 +1312,13 @@
         <v>1.158</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5288</v>
+        <v>-0.156</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5208</v>
+        <v>-0.2016</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.0456</v>
       </c>
       <c r="V11" t="n">
         <v>-0.614</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.4499</v>
+        <v>-5.1574</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.981</v>
+        <v>-4.9027</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.4689</v>
+        <v>-0.2547</v>
       </c>
       <c r="G12" t="n">
         <v>-2.2694</v>
@@ -1390,13 +1390,13 @@
         <v>1.158</v>
       </c>
       <c r="S12" t="n">
-        <v>0.7496</v>
+        <v>1.0421</v>
       </c>
       <c r="T12" t="n">
-        <v>0.7549</v>
+        <v>0.8332000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0053</v>
+        <v>0.2089</v>
       </c>
       <c r="V12" t="n">
         <v>-1.228</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>19.8497</v>
+        <v>20.74210000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>14.1489</v>
+        <v>15.0413</v>
       </c>
       <c r="F13" t="n">
-        <v>5.700500000000002</v>
+        <v>5.7006</v>
       </c>
       <c r="G13" t="n">
         <v>2.493000000000001</v>
@@ -1468,13 +1468,13 @@
         <v>17.3705</v>
       </c>
       <c r="S13" t="n">
-        <v>7.4891</v>
+        <v>8.381400000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>2.942</v>
+        <v>3.8342</v>
       </c>
       <c r="U13" t="n">
-        <v>4.547400000000001</v>
+        <v>4.5474</v>
       </c>
       <c r="V13" t="n">
         <v>3.112100000000001</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S. CAMPBELL</t>
+          <t>C. RIVERA MOTA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.6197</v>
+        <v>2.3587</v>
       </c>
       <c r="E14" t="n">
-        <v>3.7422</v>
+        <v>4.1813</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.1225</v>
+        <v>-1.8226</v>
       </c>
       <c r="G14" t="n">
-        <v>0.5927</v>
+        <v>1.9176</v>
       </c>
       <c r="H14" t="n">
-        <v>2.0408</v>
+        <v>3.3078</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.4481</v>
+        <v>-1.3902</v>
       </c>
       <c r="J14" t="n">
-        <v>3.8145</v>
+        <v>3.6379</v>
       </c>
       <c r="K14" t="n">
-        <v>3.5703</v>
+        <v>4.2897</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2442</v>
+        <v>-0.6519</v>
       </c>
       <c r="M14" t="n">
-        <v>-3.2217</v>
+        <v>-1.7203</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.5295</v>
+        <v>-0.982</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.6923</v>
+        <v>-0.7383</v>
       </c>
       <c r="P14" t="n">
-        <v>1.7371</v>
+        <v>0.965</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-0.965</v>
       </c>
       <c r="R14" t="n">
-        <v>1.7371</v>
+        <v>1.9301</v>
       </c>
       <c r="S14" t="n">
-        <v>0.618</v>
+        <v>-1.1379</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3159</v>
+        <v>-0.9052</v>
       </c>
       <c r="U14" t="n">
-        <v>0.9339</v>
+        <v>-0.2327</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.3281</v>
+        <v>0.614</v>
       </c>
       <c r="W14" t="n">
-        <v>0.2436</v>
+        <v>2.4137</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.5717</v>
+        <v>-1.7997</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>C. RIVERA MOTA</t>
+          <t>S. CAMPBELL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.4059</v>
+        <v>1.4692</v>
       </c>
       <c r="E15" t="n">
-        <v>4.2815</v>
+        <v>3.3416</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.8755</v>
+        <v>-1.8724</v>
       </c>
       <c r="G15" t="n">
-        <v>1.9176</v>
+        <v>0.5927</v>
       </c>
       <c r="H15" t="n">
-        <v>3.3078</v>
+        <v>2.0408</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.3902</v>
+        <v>-1.4481</v>
       </c>
       <c r="J15" t="n">
-        <v>3.6379</v>
+        <v>3.8145</v>
       </c>
       <c r="K15" t="n">
-        <v>4.2897</v>
+        <v>3.5703</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.6519</v>
+        <v>0.2442</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.7203</v>
+        <v>-3.2217</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.982</v>
+        <v>-1.5295</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.7383</v>
+        <v>-1.6923</v>
       </c>
       <c r="P15" t="n">
-        <v>0.965</v>
+        <v>1.7371</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.9301</v>
+        <v>1.7371</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.0907</v>
+        <v>-0.5324</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.805</v>
+        <v>-0.7165</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2856</v>
+        <v>0.184</v>
       </c>
       <c r="V15" t="n">
-        <v>0.614</v>
+        <v>-0.3281</v>
       </c>
       <c r="W15" t="n">
-        <v>2.4137</v>
+        <v>0.2436</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.7997</v>
+        <v>-0.5717</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1506</v>
+        <v>0.2903</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.8793</v>
+        <v>-0.679</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7287</v>
+        <v>0.9693000000000001</v>
       </c>
       <c r="G16" t="n">
         <v>1.5169</v>
@@ -1702,13 +1702,13 @@
         <v>0.772</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.8183</v>
+        <v>-0.3774</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7139</v>
+        <v>-0.5135999999999999</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1045</v>
+        <v>0.1361</v>
       </c>
       <c r="V16" t="n">
         <v>-0.6562</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.3948</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.2146</v>
+        <v>-0.0144</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1801</v>
+        <v>0.0872</v>
       </c>
       <c r="G17" t="n">
         <v>-0.3505</v>
@@ -1780,13 +1780,13 @@
         <v>0.579</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6233</v>
+        <v>-0.1557</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2974</v>
+        <v>-0.09719999999999999</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3259</v>
+        <v>-0.0585</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.3015</v>
+        <v>-1.4862</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.2401</v>
+        <v>-2.0399</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0614</v>
+        <v>0.5537</v>
       </c>
       <c r="G19" t="n">
         <v>0.0276</v>
@@ -1936,13 +1936,13 @@
         <v>1.3511</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.7272</v>
+        <v>-0.9118000000000001</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8328</v>
+        <v>-0.6325</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.8943</v>
+        <v>-0.2793</v>
       </c>
       <c r="V19" t="n">
         <v>0.9421</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>H. BARREIRO ESCARCEGA</t>
+          <t>D. MERKVILADZE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.7555</v>
+        <v>-3.8953</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.536</v>
+        <v>-2.2893</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.2196</v>
+        <v>-1.606</v>
       </c>
       <c r="G20" t="n">
-        <v>1.1389</v>
+        <v>-1.8159</v>
       </c>
       <c r="H20" t="n">
-        <v>0.7804</v>
+        <v>1.0609</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3584</v>
+        <v>-2.8768</v>
       </c>
       <c r="J20" t="n">
-        <v>2.2864</v>
+        <v>-0.2158</v>
       </c>
       <c r="K20" t="n">
-        <v>1.6352</v>
+        <v>1.128</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6512</v>
+        <v>-1.3438</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.1476</v>
+        <v>-1.6001</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.8548</v>
+        <v>-0.06710000000000001</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2928</v>
+        <v>-1.533</v>
       </c>
       <c r="P20" t="n">
-        <v>-2.3161</v>
+        <v>-0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.8951</v>
+        <v>-1.9301</v>
       </c>
       <c r="R20" t="n">
-        <v>0.579</v>
+        <v>1.9301</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7363</v>
+        <v>-1.4654</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0727</v>
+        <v>-0.4293</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.8091</v>
+        <v>-1.0361</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.842</v>
+        <v>-0.614</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.2859</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.842</v>
+        <v>-0.8999</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. MERKVILADZE</t>
+          <t>H. BARREIRO ESCARCEGA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.2231</v>
+        <v>-3.969</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.1891</v>
+        <v>-0.9365</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.034</v>
+        <v>-3.0325</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.8159</v>
+        <v>1.1389</v>
       </c>
       <c r="H21" t="n">
-        <v>1.0609</v>
+        <v>0.7804</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.8768</v>
+        <v>0.3584</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.2158</v>
+        <v>2.2864</v>
       </c>
       <c r="K21" t="n">
-        <v>1.128</v>
+        <v>1.6352</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.3438</v>
+        <v>0.6512</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.6001</v>
+        <v>-1.1476</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.06710000000000001</v>
+        <v>-0.8548</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.533</v>
+        <v>-0.2928</v>
       </c>
       <c r="P21" t="n">
-        <v>-0</v>
+        <v>-2.3161</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.9301</v>
+        <v>-2.8951</v>
       </c>
       <c r="R21" t="n">
-        <v>1.9301</v>
+        <v>0.579</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.7933</v>
+        <v>-0.9498</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3291</v>
+        <v>-0.3278</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.4641</v>
+        <v>-0.622</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.614</v>
+        <v>-1.842</v>
       </c>
       <c r="W21" t="n">
-        <v>0.2859</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.8999</v>
+        <v>-1.842</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.1912</v>
+        <v>-4.9169</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.2121</v>
+        <v>-3.3122</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.9791</v>
+        <v>-1.6046</v>
       </c>
       <c r="G22" t="n">
         <v>-2.13</v>
@@ -2170,13 +2170,13 @@
         <v>0.772</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3893</v>
+        <v>-0.115</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2102</v>
+        <v>-0.3103</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1792</v>
+        <v>0.1953</v>
       </c>
       <c r="V22" t="n">
         <v>-1.5138</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-8.279500000000001</v>
+        <v>-7.8591</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.488</v>
+        <v>-2.9873</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.7916</v>
+        <v>-4.8719</v>
       </c>
       <c r="G23" t="n">
         <v>-3.6576</v>
@@ -2248,13 +2248,13 @@
         <v>0.965</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.0477</v>
+        <v>-0.6273</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.1157</v>
+        <v>-0.615</v>
       </c>
       <c r="U23" t="n">
-        <v>0.068</v>
+        <v>-0.0123</v>
       </c>
       <c r="V23" t="n">
         <v>0.2859</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-19.8496</v>
+        <v>-18.5144</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.700499999999999</v>
+        <v>-5.700699999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>-14.1491</v>
+        <v>-12.8138</v>
       </c>
       <c r="G24" t="n">
         <v>-2.4933</v>
@@ -2326,13 +2326,13 @@
         <v>10.6154</v>
       </c>
       <c r="S24" t="n">
-        <v>-7.4891</v>
+        <v>-6.153700000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>-4.5473</v>
+        <v>-4.5474</v>
       </c>
       <c r="U24" t="n">
-        <v>-2.9418</v>
+        <v>-1.6065</v>
       </c>
       <c r="V24" t="n">
         <v>-3.1121</v>
